--- a/Models/КРС/results/КРС - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>348.02</v>
+        <v>318.48</v>
       </c>
       <c r="C2" t="n">
-        <v>328.23</v>
+        <v>289.78</v>
       </c>
       <c r="D2" t="n">
-        <v>11.16</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>746.59</v>
+        <v>527.97</v>
       </c>
       <c r="C3" t="n">
-        <v>682.5700000000001</v>
+        <v>462.49</v>
       </c>
       <c r="D3" t="n">
-        <v>13.06</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2458.44</v>
+        <v>1325.38</v>
       </c>
       <c r="C4" t="n">
-        <v>2115.42</v>
+        <v>1131.2</v>
       </c>
       <c r="D4" t="n">
-        <v>29.88</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>345.15</v>
+        <v>383.52</v>
       </c>
       <c r="C5" t="n">
-        <v>316.49</v>
+        <v>348.61</v>
       </c>
       <c r="D5" t="n">
-        <v>17.81</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1381.16</v>
+        <v>594.72</v>
       </c>
       <c r="C6" t="n">
-        <v>1302.79</v>
+        <v>540.54</v>
       </c>
       <c r="D6" t="n">
-        <v>35.06</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="7">
@@ -537,14 +537,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.85</v>
+        <v>11.13</v>
       </c>
       <c r="C7" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="D7" t="n">
-        <v>89.48</v>
-      </c>
+        <v>8.34</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="C8" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="D8" t="n">
-        <v>26.3</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>267.62</v>
+        <v>184.02</v>
       </c>
       <c r="C9" t="n">
-        <v>228.59</v>
+        <v>164.59</v>
       </c>
       <c r="D9" t="n">
-        <v>46.33</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>690.85</v>
+        <v>1268.03</v>
       </c>
       <c r="C10" t="n">
-        <v>512.64</v>
+        <v>894.39</v>
       </c>
       <c r="D10" t="n">
-        <v>10.74</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>272.98</v>
+        <v>205.36</v>
       </c>
       <c r="C11" t="n">
-        <v>227.11</v>
+        <v>162.47</v>
       </c>
       <c r="D11" t="n">
-        <v>5.69</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>854.09</v>
+        <v>596.79</v>
       </c>
       <c r="C12" t="n">
-        <v>776.11</v>
+        <v>537.5599999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>22.68</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1064.95</v>
+        <v>349.58</v>
       </c>
       <c r="C13" t="n">
-        <v>814.28</v>
+        <v>282.55</v>
       </c>
       <c r="D13" t="n">
-        <v>20.16</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>117.24</v>
+        <v>190.06</v>
       </c>
       <c r="C14" t="n">
-        <v>107.67</v>
+        <v>157.73</v>
       </c>
       <c r="D14" t="n">
-        <v>6.77</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80.64</v>
+        <v>141.49</v>
       </c>
       <c r="C15" t="n">
-        <v>63.09</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>34.55</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1897.54</v>
+        <v>1917.32</v>
       </c>
       <c r="C16" t="n">
-        <v>1540.82</v>
+        <v>1527.36</v>
       </c>
       <c r="D16" t="n">
-        <v>37.86</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3169.05</v>
+        <v>2294.51</v>
       </c>
       <c r="C17" t="n">
-        <v>2779.67</v>
+        <v>1992.8</v>
       </c>
       <c r="D17" t="n">
-        <v>62.62</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>524.03</v>
+        <v>777.27</v>
       </c>
       <c r="C18" t="n">
-        <v>406.73</v>
+        <v>603.52</v>
       </c>
       <c r="D18" t="n">
-        <v>94.19</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>684.38</v>
+        <v>484.74</v>
       </c>
       <c r="C19" t="n">
-        <v>591.9</v>
+        <v>414.12</v>
       </c>
       <c r="D19" t="n">
-        <v>14.39</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>333.59</v>
+        <v>384.96</v>
       </c>
       <c r="C20" t="n">
-        <v>272.6</v>
+        <v>321.99</v>
       </c>
       <c r="D20" t="n">
-        <v>11.59</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4168.12</v>
+        <v>4063.44</v>
       </c>
       <c r="C21" t="n">
-        <v>2975.2</v>
+        <v>2945.1</v>
       </c>
       <c r="D21" t="n">
-        <v>21.88</v>
+        <v>21.59</v>
       </c>
     </row>
   </sheetData>
